--- a/04_DESIGN_TABLES/DesignTable_6401.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6401.xlsx
@@ -1468,7 +1468,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -1476,7 +1476,11 @@
           <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source)</t>
         </is>
       </c>
-      <c r="T13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L29@DRIVE=1.36~1.360; HEXB@HEX=0.88~0.875; D3@BORE=0.39~0.391; D4@BORE=0.41~0.406</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1550,7 +1554,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -1558,7 +1562,11 @@
           <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source)</t>
         </is>
       </c>
-      <c r="T14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L29@DRIVE=1.55~1.550; HEXB@HEX=0.88~0.875; D3@BORE=0.39~0.391; D4@BORE=0.53~0.531</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1878,7 +1886,7 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -1886,7 +1894,11 @@
           <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source)</t>
         </is>
       </c>
-      <c r="T18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L29@DRIVE=1.76~1.760; HEXB@HEX=1.13~1.125; D3@BORE=0.48~0.484; D4@BORE=0.72~0.719</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2042,7 +2054,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -2050,7 +2062,11 @@
           <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source)</t>
         </is>
       </c>
-      <c r="T20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L29@DRIVE=1.84~1.840; HEXB@HEX=1.25~1.250; D3@BORE=0.61~0.609; D4@BORE=0.53~0.531</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2124,7 +2140,7 @@
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
@@ -2134,7 +2150,7 @@
       </c>
       <c r="T21" s="4" t="inlineStr">
         <is>
-          <t>L29=1.73 &lt; 12-8 (1.84) - non-monotonic, as-printed</t>
+          <t>L29=1.73 &lt; 12-8 (1.84) - non-monotonic, as-printed | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L29@DRIVE=1.73~1.730; HEXB@HEX=1.25~1.250; D3@BORE=0.61~0.609; D4@BORE=0.72~0.719</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6401.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6401.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0.5600000000000001</v>
@@ -657,10 +657,14 @@
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1700 Overall Length = 1.040 (table had 1.05) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr"/>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1700 Overall Length = 1.040 (table had 1.05) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.05 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.04) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.04 -&gt; Air-Way 1.05</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -679,7 +683,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0.5600000000000001</v>
@@ -739,10 +743,14 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1701 Overall Length = 1.250 (table had 1.23) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr"/>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1701 Overall Length = 1.250 (table had 1.23) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.23 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.25) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.25 -&gt; Air-Way 1.23</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1085,7 +1093,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0.6899999999999999</v>
@@ -1145,10 +1153,14 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1702 Overall Length = 1.290 (table had 1.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="T9" s="3" t="inlineStr"/>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1702 Overall Length = 1.290 (table had 1.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.3 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.29) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.29 -&gt; Air-Way 1.3</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1167,10 +1179,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.5625</v>
@@ -1227,10 +1239,14 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1703 Overall Length = 1.260 (table had 1.3); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1703 Hex Flat = 0.813 (table had 0.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="T10" s="3" t="inlineStr"/>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1703 Overall Length = 1.260 (table had 1.3); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1703 Hex Flat = 0.813 (table had 0.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.3 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.26) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; HEXB@HEX: Air-Way 0.75 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.813) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.26 -&gt; Air-Way 1.3 | 2026-10-20 Air-Way first: HEXB@HEX OMi/Brennan 0.813 -&gt; Air-Way 0.75</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1249,7 +1265,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>0.88</v>
@@ -1309,10 +1325,14 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1704 Overall Length = 1.540 (table had 1.48) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="inlineStr"/>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1704 Overall Length = 1.540 (table had 1.48) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.48 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.54) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.54 -&gt; Air-Way 1.48</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1331,7 +1351,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0.88</v>
@@ -1391,10 +1411,14 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1705 Overall Length = 1.360 (table had 1.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr"/>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1705 Overall Length = 1.360 (table had 1.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.25 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.36) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.36 -&gt; Air-Way 1.25</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1585,10 +1609,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1.062</v>
+        <v>1.13</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0.75</v>
@@ -1645,10 +1669,14 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1708 Overall Length = 1.760 (table had 1.77); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1708 Hex Flat = 1.062 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="inlineStr"/>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1708 Overall Length = 1.760 (table had 1.77); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1708 Hex Flat = 1.062 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.77 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.76) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; HEXB@HEX: Air-Way 1.13 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.062) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.76 -&gt; Air-Way 1.77 | 2026-10-20 Air-Way first: HEXB@HEX OMi/Brennan 1.062 -&gt; Air-Way 1.13</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1667,7 +1695,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>1</v>
@@ -1727,10 +1755,14 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1709 Overall Length = 1.460 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="T16" s="3" t="inlineStr"/>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1709 Overall Length = 1.460 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.5 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.46) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.46 -&gt; Air-Way 1.5</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1749,7 +1781,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>1</v>
@@ -1809,10 +1841,14 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1710 Overall Length = 1.650 (table had 1.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr"/>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1710 Overall Length = 1.650 (table had 1.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.69 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.65) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.65 -&gt; Air-Way 1.69</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1917,7 +1953,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>1.25</v>
@@ -1977,10 +2013,14 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1712 Overall Length = 1.620 (table had 1.66) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr"/>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1712 Overall Length = 1.620 (table had 1.66) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.66 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.62) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.62 -&gt; Air-Way 1.66</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2171,7 +2211,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>1.38</v>
@@ -2231,10 +2271,14 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1715 Overall Length = 2.120 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr"/>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1715 Overall Length = 2.120 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 2.03 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.12) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 2.12 -&gt; Air-Way 2.03</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2253,7 +2297,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>1.5</v>
@@ -2313,10 +2357,14 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1716 Overall Length = 1.960 (table had 1.87) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="T23" s="3" t="inlineStr"/>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1716 Overall Length = 1.960 (table had 1.87) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 1.87 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.96) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="T23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 1.96 -&gt; Air-Way 1.87</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2335,7 +2383,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>1.5</v>
@@ -2395,10 +2443,14 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1717 Overall Length = 2.120 (table had 2.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="T24" s="3" t="inlineStr"/>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1717 Overall Length = 2.120 (table had 2.06) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 2.06 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.12) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 2.12 -&gt; Air-Way 2.06</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2417,7 +2469,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>1.88</v>
@@ -2477,10 +2529,14 @@
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1720 Overall Length = 2.160 (table had 2.17) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr"/>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1720 Overall Length = 2.160 (table had 2.17) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 2.17 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.16) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 2.16 -&gt; Air-Way 2.17</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2580,7 +2636,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>2.13</v>
@@ -2640,10 +2696,14 @@
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1722 Overall Length = 2.280 (table had 2.27) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="inlineStr"/>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1722 Overall Length = 2.280 (table had 2.27) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 2.27 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.28) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 2.28 -&gt; Air-Way 2.27</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2662,7 +2722,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="C28" s="5" t="n">
         <v>2.75</v>
@@ -2720,12 +2780,12 @@
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1723 Overall Length = 2.480 (table had 2.47) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>ORB end: ORD-5700+measured grooves+MS51527 J2; NPTF end: measured (validated); L29/hex: Air-Way (single source); L29@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1723 Overall Length = 2.480 (table had 2.47) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L29@DRIVE: Air-Way 2.47 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.48) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>ORB -32 groove width unmeasured</t>
+          <t>ORB -32 groove width unmeasured | 2026-10-20 Air-Way first: L29@DRIVE OMi/Brennan 2.48 -&gt; Air-Way 2.47</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
